--- a/output/pdf_financials_xlsx/OGO.xlsx
+++ b/output/pdf_financials_xlsx/OGO.xlsx
@@ -5856,43 +5856,43 @@
         <v>2.458257</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.1634</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.069578</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.36387</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.215087</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.126939</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.16027</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.367396</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.737436</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.604958</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.394988</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.032465</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.931527000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.575436</v>
       </c>
     </row>
     <row r="93">
@@ -10034,7 +10034,11 @@
           <t>Reserves (note 15(f))</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11751,7 +11755,11 @@
           <t>Reserves (note 18(f))</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13864,7 +13872,11 @@
           <t>Reserves (note 17(f))</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15757,7 +15769,11 @@
           <t>Reserves (note 13(f))</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17272,7 +17288,11 @@
           <t>Reserves (note 16(e))</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19197,7 +19217,11 @@
           <t>Reserves (note 15(f))</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20504,7 +20528,11 @@
           <t>Reserves (note 13g)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -22336,7 +22364,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23738,7 +23770,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OGO.xlsx
+++ b/output/pdf_financials_xlsx/OGO.xlsx
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.187454</v>
+        <v>0.090902</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.274282</v>
@@ -931,10 +931,10 @@
         <v>0.07771</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.215067</v>
+        <v>0.096552</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.408874</v>
+        <v>0.991314</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.492407</v>
@@ -992,7 +992,7 @@
         <v>-1.652744</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.786764</v>
+        <v>-1.369204</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-3.323352</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002815</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004517</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.510976</v>
+        <v>-0.513791</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.935074</v>
+        <v>-1.939591</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.467593</v>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.510976</v>
+        <v>-0.513791</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.935074</v>
+        <v>-1.939591</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.467593</v>
@@ -2358,55 +2358,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.427914</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.205832</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.055627</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.060319</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.042757</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.10009</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.044791</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.063211</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.02623</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.172025</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.18902</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.054565</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>11.869999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.769979</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.186295</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.291174</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>5.712283</v>
       </c>
     </row>
     <row r="35">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.427914</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.205832</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.055627</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.060319</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.042757</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.10009</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.044791</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.063211</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.02623</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.172025</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.18902</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.054565</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>11.869999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.769979</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.186295</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.291174</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>5.712283</v>
       </c>
     </row>
     <row r="37">
@@ -3170,37 +3170,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.506603</v>
+        <v>1.078689</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.231352</v>
+        <v>0.02552</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.08829099999999999</v>
+        <v>0.032664</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.172657</v>
+        <v>0.112338</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.068859</v>
+        <v>0.026102</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.133737</v>
+        <v>0.033647</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.908361</v>
+        <v>0.84515</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.07771400000000001</v>
+        <v>0.051484</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.614718</v>
+        <v>0.442693</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.199138</v>
+        <v>1.010118</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -72933,7 +72933,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -73923,7 +73923,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -77093,7 +77093,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -78877,7 +78877,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -79079,7 +79079,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E708" s="5" t="n">
@@ -79578,7 +79578,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E713" s="5" t="n">

--- a/output/pdf_financials_xlsx/OGO.xlsx
+++ b/output/pdf_financials_xlsx/OGO.xlsx
@@ -742,22 +742,22 @@
         <v>0.07109</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.116359</v>
+        <v>0.161359</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.107046</v>
+        <v>0.144546</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.110104</v>
+        <v>0.146104</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.068048</v>
+        <v>0.104048</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.07771</v>
+        <v>0.12471</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.027613</v>
+        <v>0.06612899999999999</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.134592</v>
@@ -916,19 +916,19 @@
         <v>0.07109</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.116359</v>
+        <v>0.161359</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.107046</v>
+        <v>0.144546</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.110104</v>
+        <v>0.146104</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.068048</v>
+        <v>0.104048</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.07771</v>
+        <v>0.12471</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.096552</v>
@@ -1582,19 +1582,19 @@
         <v>-0.224709</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.007615</v>
+        <v>-1.793938</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.021892</v>
+        <v>-4.477046</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-9.441848999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-5.50218</v>
+        <v>-5.252339</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.010411</v>
+        <v>-2.547098</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-6.340664</v>
@@ -1603,10 +1603,10 @@
         <v>-10.828211</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-13.427223</v>
+        <v>-5.627894</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-1.973192</v>
+        <v>-3.150144</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-16.822166</v>
@@ -1640,19 +1640,19 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.007615</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>0.021892</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.249841</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>2.557509</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>0</v>
+        <v>0.898828</v>
       </c>
       <c r="P60" s="3" t="n">
         <v>0.898828</v>
@@ -6845,16 +6845,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.028572</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.269539</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.320764</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.231418</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -51773,7 +51773,11 @@
           <t>Private placement (note 6a)</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -54678,7 +54682,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E461" s="5" t="n">
         <v>0.028572</v>
       </c>
@@ -55658,7 +55666,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E471" s="5" t="n">
         <v>1.80225</v>
       </c>
@@ -60000,7 +60012,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -62313,7 +62329,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -67704,7 +67724,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -67803,7 +67827,11 @@
           <t>Gain (loss) from discontinued operations (note 10)</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -71949,7 +71977,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
@@ -72042,7 +72074,11 @@
           <t>Net income from discontinued operations</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E637" t="inlineStr">
         <is>
           <t>-</t>
@@ -73325,7 +73361,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -74226,7 +74262,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -74727,7 +74767,11 @@
           <t>Directors fees (note 7)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>
@@ -76101,7 +76145,11 @@
           <t>Directors fees (note 9)</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E678" t="inlineStr">
         <is>
           <t>-</t>
@@ -76992,7 +77040,11 @@
           <t>Director fees (note 11)</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
           <t>-</t>
@@ -78776,7 +78828,11 @@
           <t>Director fees (note 9)</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E705" t="inlineStr">
         <is>
           <t>-</t>
@@ -79475,7 +79531,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
